--- a/PATXOT 512/marzo/PATXOT 521 MARZO.xlsx
+++ b/PATXOT 512/marzo/PATXOT 521 MARZO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PATXOT 512\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PATXOT 512\marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06AF104B-C00E-4164-B1B2-207607294718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC88B20-91DE-4FDD-ACF4-003B56448561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -2205,7 +2205,7 @@
         <v>63</v>
       </c>
       <c r="C17" s="170">
-        <v>74825.289999999994</v>
+        <v>88943.14</v>
       </c>
       <c r="D17" s="48"/>
       <c r="F17" s="14"/>
@@ -2229,7 +2229,7 @@
       <c r="B20" s="90"/>
       <c r="C20" s="61">
         <f>SUM(C17:C19)</f>
-        <v>74825.289999999994</v>
+        <v>88943.14</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2276,9 +2276,7 @@
         <v>127</v>
       </c>
       <c r="B26" s="88"/>
-      <c r="C26" s="86">
-        <v>150000</v>
-      </c>
+      <c r="C26" s="86"/>
       <c r="D26" s="5"/>
       <c r="E26" s="14"/>
       <c r="F26" s="22"/>
@@ -2288,7 +2286,7 @@
       <c r="B27" s="90"/>
       <c r="C27" s="61">
         <f>SUM(C21:C26)</f>
-        <v>216534.6</v>
+        <v>66534.600000000006</v>
       </c>
       <c r="F27" s="22"/>
     </row>
@@ -2299,7 +2297,7 @@
       <c r="B28" s="80"/>
       <c r="C28" s="93">
         <f>+C27+C20</f>
-        <v>291359.89</v>
+        <v>155477.74</v>
       </c>
       <c r="F28" s="22"/>
     </row>
@@ -2354,7 +2352,7 @@
       <c r="B37" s="34"/>
       <c r="C37" s="35">
         <f>+C35+C28</f>
-        <v>291359.89</v>
+        <v>155477.74</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2371,7 +2369,7 @@
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="146">
-        <v>-225247.17452636751</v>
+        <v>-132285.39625966031</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -2382,7 +2380,7 @@
       </c>
       <c r="C41" s="32">
         <f>'prorrateo '!F15</f>
-        <v>234321.66826670722</v>
+        <v>291359.89</v>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
@@ -2404,7 +2402,7 @@
       </c>
       <c r="C43" s="94">
         <f>-(C28-C26)</f>
-        <v>-141359.89000000001</v>
+        <v>-155477.74</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2414,7 +2412,7 @@
       <c r="B44" s="33"/>
       <c r="C44" s="40">
         <f>SUM(C40:C43)</f>
-        <v>-132285.39625966031</v>
+        <v>3596.7537403397146</v>
       </c>
       <c r="D44" s="6"/>
     </row>
@@ -2532,7 +2530,7 @@
         <v>49</v>
       </c>
       <c r="E1" s="50">
-        <v>291359.89</v>
+        <v>155477.74</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -2620,11 +2618,11 @@
       </c>
       <c r="D5" s="59"/>
       <c r="E5" s="150">
-        <v>31310.712786555188</v>
+        <v>40207.664820000005</v>
       </c>
       <c r="F5" s="151">
         <f t="shared" ref="F5:F9" si="0">E5</f>
-        <v>31310.712786555188</v>
+        <v>40207.664820000005</v>
       </c>
       <c r="G5" s="152">
         <f>E5-F5</f>
@@ -2639,7 +2637,7 @@
       </c>
       <c r="J5" s="97">
         <f>E$1*I5/100</f>
-        <v>40207.664820000005</v>
+        <v>21455.92812</v>
       </c>
       <c r="K5" s="143">
         <f>edesur!H5</f>
@@ -2647,7 +2645,7 @@
       </c>
       <c r="L5" s="104">
         <f>G5+H5+J5+K5</f>
-        <v>40207.664820000005</v>
+        <v>21455.92812</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
@@ -2662,11 +2660,11 @@
         <v>72</v>
       </c>
       <c r="E6" s="150">
-        <v>30871.318343297658</v>
+        <v>34555.282954000002</v>
       </c>
       <c r="F6" s="151">
         <f t="shared" si="0"/>
-        <v>30871.318343297658</v>
+        <v>34555.282954000002</v>
       </c>
       <c r="G6" s="152">
         <f t="shared" ref="G6:G14" si="1">E6-F6</f>
@@ -2681,7 +2679,7 @@
       </c>
       <c r="J6" s="97">
         <f t="shared" ref="J6:J14" si="3">E$1*I6/100</f>
-        <v>34555.282954000002</v>
+        <v>18439.659963999999</v>
       </c>
       <c r="K6" s="143">
         <f>edesur!H6</f>
@@ -2689,7 +2687,7 @@
       </c>
       <c r="L6" s="104">
         <f t="shared" ref="L6:L14" si="4">G6+H6+J6+K6</f>
-        <v>34555.282954000002</v>
+        <v>18439.659963999999</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
@@ -2704,11 +2702,11 @@
         <v>73</v>
       </c>
       <c r="E7" s="150">
-        <v>31575.545756876258</v>
+        <v>36303.442294000008</v>
       </c>
       <c r="F7" s="151">
         <f t="shared" si="0"/>
-        <v>31575.545756876258</v>
+        <v>36303.442294000008</v>
       </c>
       <c r="G7" s="152">
         <f t="shared" si="1"/>
@@ -2723,7 +2721,7 @@
       </c>
       <c r="J7" s="97">
         <f t="shared" si="3"/>
-        <v>36303.442294000008</v>
+        <v>19372.526404</v>
       </c>
       <c r="K7" s="143">
         <f>edesur!H7</f>
@@ -2731,7 +2729,7 @@
       </c>
       <c r="L7" s="104">
         <f t="shared" si="4"/>
-        <v>36303.442294000008</v>
+        <v>19372.526404</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
@@ -2746,11 +2744,11 @@
         <v>74</v>
       </c>
       <c r="E8" s="150">
-        <v>36252.089402090307</v>
+        <v>42975.583775000006</v>
       </c>
       <c r="F8" s="151">
         <f t="shared" si="0"/>
-        <v>36252.089402090307</v>
+        <v>42975.583775000006</v>
       </c>
       <c r="G8" s="152">
         <f t="shared" si="1"/>
@@ -2765,7 +2763,7 @@
       </c>
       <c r="J8" s="97">
         <f t="shared" si="3"/>
-        <v>42975.583775000006</v>
+        <v>22932.966650000002</v>
       </c>
       <c r="K8" s="143">
         <f>edesur!H8</f>
@@ -2773,7 +2771,7 @@
       </c>
       <c r="L8" s="104">
         <f t="shared" si="4"/>
-        <v>42975.583775000006</v>
+        <v>22932.966650000002</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -2788,11 +2786,11 @@
         <v>75</v>
       </c>
       <c r="E9" s="150">
-        <v>26179.162034284283</v>
+        <v>36157.762348999997</v>
       </c>
       <c r="F9" s="151">
         <f t="shared" si="0"/>
-        <v>26179.162034284283</v>
+        <v>36157.762348999997</v>
       </c>
       <c r="G9" s="152">
         <f t="shared" si="1"/>
@@ -2807,7 +2805,7 @@
       </c>
       <c r="J9" s="97">
         <f t="shared" si="3"/>
-        <v>36157.762348999997</v>
+        <v>19294.787533999999</v>
       </c>
       <c r="K9" s="143">
         <f>edesur!H9</f>
@@ -2815,7 +2813,7 @@
       </c>
       <c r="L9" s="104">
         <f>G9+H9+J9+K9</f>
-        <v>36157.762348999997</v>
+        <v>19294.787533999999</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2828,11 +2826,11 @@
       </c>
       <c r="D10" s="73"/>
       <c r="E10" s="150">
-        <v>26422.052583705688</v>
+        <v>36361.714272000005</v>
       </c>
       <c r="F10" s="151">
         <f>E10</f>
-        <v>26422.052583705688</v>
+        <v>36361.714272000005</v>
       </c>
       <c r="G10" s="152">
         <f t="shared" si="1"/>
@@ -2847,7 +2845,7 @@
       </c>
       <c r="J10" s="97">
         <f t="shared" si="3"/>
-        <v>36361.714272000005</v>
+        <v>19403.621952000001</v>
       </c>
       <c r="K10" s="143">
         <f>edesur!H10</f>
@@ -2855,7 +2853,7 @@
       </c>
       <c r="L10" s="104">
         <f t="shared" si="4"/>
-        <v>36361.714272000005</v>
+        <v>19403.621952000001</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2868,11 +2866,11 @@
       </c>
       <c r="D11" s="73"/>
       <c r="E11" s="150">
-        <v>39198.725671190645</v>
+        <v>53202.315914000006</v>
       </c>
       <c r="F11" s="151">
         <f>E11</f>
-        <v>39198.725671190645</v>
+        <v>53202.315914000006</v>
       </c>
       <c r="G11" s="152">
         <f t="shared" si="1"/>
@@ -2887,7 +2885,7 @@
       </c>
       <c r="J11" s="97">
         <f t="shared" si="3"/>
-        <v>53202.315914000006</v>
+        <v>28390.235323999997</v>
       </c>
       <c r="K11" s="143">
         <f>edesur!H11</f>
@@ -2895,7 +2893,7 @@
       </c>
       <c r="L11" s="104">
         <f t="shared" si="4"/>
-        <v>53202.315914000006</v>
+        <v>28390.235323999997</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2909,11 +2907,11 @@
       </c>
       <c r="D12" s="73"/>
       <c r="E12" s="150">
-        <v>4212.6036841376008</v>
+        <v>3904.2225260000005</v>
       </c>
       <c r="F12" s="151">
         <f t="shared" ref="F12:F14" si="5">E12</f>
-        <v>4212.6036841376008</v>
+        <v>3904.2225260000005</v>
       </c>
       <c r="G12" s="152">
         <f t="shared" si="1"/>
@@ -2928,14 +2926,14 @@
       </c>
       <c r="J12" s="97">
         <f t="shared" si="3"/>
-        <v>3904.2225260000005</v>
+        <v>2083.4017159999999</v>
       </c>
       <c r="K12" s="143">
         <v>0</v>
       </c>
       <c r="L12" s="104">
         <f t="shared" si="4"/>
-        <v>3904.2225260000005</v>
+        <v>2083.4017159999999</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2949,11 +2947,11 @@
       </c>
       <c r="D13" s="73"/>
       <c r="E13" s="150">
-        <v>4149.7290022848001</v>
+        <v>3845.9505480000003</v>
       </c>
       <c r="F13" s="151">
         <f t="shared" si="5"/>
-        <v>4149.7290022848001</v>
+        <v>3845.9505480000003</v>
       </c>
       <c r="G13" s="152">
         <f t="shared" si="1"/>
@@ -2968,14 +2966,14 @@
       </c>
       <c r="J13" s="97">
         <f t="shared" si="3"/>
-        <v>3845.9505480000003</v>
+        <v>2052.3061680000001</v>
       </c>
       <c r="K13" s="143">
         <v>0</v>
       </c>
       <c r="L13" s="104">
         <f t="shared" si="4"/>
-        <v>3845.9505480000003</v>
+        <v>2052.3061680000001</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2989,11 +2987,11 @@
       </c>
       <c r="D14" s="73"/>
       <c r="E14" s="150">
-        <v>4149.7290022848001</v>
+        <v>3845.9505480000003</v>
       </c>
       <c r="F14" s="151">
         <f t="shared" si="5"/>
-        <v>4149.7290022848001</v>
+        <v>3845.9505480000003</v>
       </c>
       <c r="G14" s="152">
         <f t="shared" si="1"/>
@@ -3008,14 +3006,14 @@
       </c>
       <c r="J14" s="97">
         <f t="shared" si="3"/>
-        <v>3845.9505480000003</v>
+        <v>2052.3061680000001</v>
       </c>
       <c r="K14" s="143">
         <v>0</v>
       </c>
       <c r="L14" s="104">
         <f t="shared" si="4"/>
-        <v>3845.9505480000003</v>
+        <v>2052.3061680000001</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3027,11 +3025,11 @@
       <c r="D15" s="107"/>
       <c r="E15" s="42">
         <f>SUM(E5:E14)</f>
-        <v>234321.66826670722</v>
+        <v>291359.89</v>
       </c>
       <c r="F15" s="108">
         <f>SUM(F5:F14)</f>
-        <v>234321.66826670722</v>
+        <v>291359.89</v>
       </c>
       <c r="G15" s="108"/>
       <c r="H15" s="109">
@@ -3044,7 +3042,7 @@
       </c>
       <c r="J15" s="39">
         <f>SUM(J5:J14)</f>
-        <v>291359.89</v>
+        <v>155477.74000000002</v>
       </c>
       <c r="K15" s="42">
         <f>SUM(K5:K11)</f>
@@ -3052,7 +3050,7 @@
       </c>
       <c r="L15" s="42">
         <f>SUM(L5:L14)</f>
-        <v>291359.89</v>
+        <v>155477.74000000002</v>
       </c>
     </row>
     <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
@@ -3619,7 +3617,7 @@
       <c r="I42" s="158"/>
       <c r="J42" s="164">
         <f>J7</f>
-        <v>36303.442294000008</v>
+        <v>19372.526404</v>
       </c>
       <c r="K42" s="156"/>
       <c r="L42" s="155"/>
@@ -3778,7 +3776,7 @@
       <c r="I52" s="197"/>
       <c r="J52" s="198">
         <f>SUM(J42:J51)</f>
-        <v>36379.242294000011</v>
+        <v>19448.326404000003</v>
       </c>
       <c r="K52" s="188"/>
       <c r="L52" s="168"/>
@@ -3937,7 +3935,7 @@
       <c r="I66" s="158"/>
       <c r="J66" s="164">
         <f>J8</f>
-        <v>42975.583775000006</v>
+        <v>22932.966650000002</v>
       </c>
       <c r="K66" s="156"/>
       <c r="L66" s="155"/>
@@ -4061,7 +4059,7 @@
       <c r="I76" s="197"/>
       <c r="J76" s="198">
         <f>SUM(J66:J75)</f>
-        <v>42975.583775000006</v>
+        <v>22932.966650000002</v>
       </c>
       <c r="K76" s="188"/>
       <c r="L76" s="168"/>
@@ -4214,7 +4212,7 @@
       <c r="I93" s="158"/>
       <c r="J93" s="164">
         <f>J10</f>
-        <v>36361.714272000005</v>
+        <v>19403.621952000001</v>
       </c>
       <c r="K93" s="156"/>
       <c r="L93" s="155"/>
@@ -4337,7 +4335,7 @@
       <c r="I103" s="197"/>
       <c r="J103" s="198">
         <f>SUM(J93:J102)</f>
-        <v>36385.604272000004</v>
+        <v>19427.511952000001</v>
       </c>
       <c r="K103" s="188"/>
       <c r="L103" s="168"/>
@@ -4490,7 +4488,7 @@
       <c r="I118" s="158"/>
       <c r="J118" s="164">
         <f>J5</f>
-        <v>40207.664820000005</v>
+        <v>21455.92812</v>
       </c>
       <c r="K118" s="156"/>
       <c r="L118" s="155"/>
@@ -4614,7 +4612,7 @@
       <c r="I128" s="197"/>
       <c r="J128" s="198">
         <f>SUM(J118:J127)</f>
-        <v>40155.324820000009</v>
+        <v>21403.58812</v>
       </c>
       <c r="K128" s="188"/>
       <c r="L128" s="168"/>
